--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.94053224761916</v>
+        <v>6.977836490238114</v>
       </c>
       <c r="D2" t="n">
-        <v>42.87501202661007</v>
+        <v>6.967189454324136</v>
       </c>
       <c r="E2" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F2" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.03323327113053</v>
+        <v>6.992900406558711</v>
       </c>
       <c r="D3" t="n">
-        <v>41.6123624860531</v>
+        <v>6.762008903983629</v>
       </c>
       <c r="E3" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F3" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.57155974952638</v>
+        <v>7.567878459298037</v>
       </c>
       <c r="D4" t="n">
-        <v>39.33367946419512</v>
+        <v>6.391722912931708</v>
       </c>
       <c r="E4" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F4" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.28282367592168</v>
+        <v>5.570958847337274</v>
       </c>
       <c r="D5" t="n">
-        <v>35.05183469864905</v>
+        <v>5.69592313853047</v>
       </c>
       <c r="E5" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F5" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.27648280500288</v>
+        <v>4.919928455812967</v>
       </c>
       <c r="D6" t="n">
-        <v>31.40098564492548</v>
+        <v>5.102660167300392</v>
       </c>
       <c r="E6" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F6" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.93393525631722</v>
+        <v>2.914264479151548</v>
       </c>
       <c r="D7" t="n">
-        <v>11.98419849492826</v>
+        <v>1.947432255425842</v>
       </c>
       <c r="E7" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F7" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.25553093003925</v>
+        <v>2.966523776131379</v>
       </c>
       <c r="D8" t="n">
-        <v>18.36441875383775</v>
+        <v>2.984218047498635</v>
       </c>
       <c r="E8" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F8" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.75653047435859</v>
+        <v>1.747936202083271</v>
       </c>
       <c r="D9" t="n">
-        <v>24.25766699813462</v>
+        <v>3.941870887196876</v>
       </c>
       <c r="E9" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F9" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.298336422387736</v>
+        <v>1.510979668638007</v>
       </c>
       <c r="D10" t="n">
-        <v>34.57320536941351</v>
+        <v>5.618145872529697</v>
       </c>
       <c r="E10" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F10" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>11.14741866566127</v>
+        <v>1.811455533169957</v>
       </c>
       <c r="D11" t="n">
-        <v>26.20422461119163</v>
+        <v>4.258186499318641</v>
       </c>
       <c r="E11" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F11" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>1.645232543884534</v>
+        <v>0.2673502883812368</v>
       </c>
       <c r="D12" t="n">
-        <v>1.414213562373095</v>
+        <v>0.229809703885628</v>
       </c>
       <c r="E12" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F12" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.2900985839871</v>
+        <v>2.484641019897904</v>
       </c>
       <c r="D13" t="n">
-        <v>22.5539178371942</v>
+        <v>3.665011648544058</v>
       </c>
       <c r="E13" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F13" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>22.08854975799321</v>
+        <v>3.589389335673896</v>
       </c>
       <c r="D14" t="n">
-        <v>23.88067264442627</v>
+        <v>3.880609304719269</v>
       </c>
       <c r="E14" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F14" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>24.67499459608647</v>
+        <v>4.009686621864051</v>
       </c>
       <c r="D15" t="n">
-        <v>28.69233347080715</v>
+        <v>4.662504189006161</v>
       </c>
       <c r="E15" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F15" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>32.59320322979064</v>
+        <v>5.296395524840979</v>
       </c>
       <c r="D16" t="n">
-        <v>31.79226845747063</v>
+        <v>5.166243624338978</v>
       </c>
       <c r="E16" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F16" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94155852679729</v>
+        <v>5.678003260604561</v>
       </c>
       <c r="D17" t="n">
-        <v>34.34999468193651</v>
+        <v>5.581874135814684</v>
       </c>
       <c r="E17" t="n">
-        <v>13.15008454849562</v>
+        <v>2.136888739130538</v>
       </c>
       <c r="F17" t="n">
-        <v>10.64984002206293</v>
+        <v>1.730599003585226</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
